--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\TREINAMENTO\src\test\resources\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D76439-CC9C-46F5-84F3-D5FA12FD50D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB5C55E-2D61-448B-9643-1957C93D0AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="45" windowWidth="17715" windowHeight="10740" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="22245" windowHeight="15585" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
-    <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
-    <sheet name="USUARIO_SECUNDARIO" sheetId="2" r:id="rId2"/>
+    <sheet name="EBAC_MASSAS" sheetId="3" r:id="rId1"/>
+    <sheet name="USUARIO" sheetId="1" r:id="rId2"/>
+    <sheet name="USUARIO_SECUNDARIO" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="60">
   <si>
     <t>TAG</t>
   </si>
@@ -178,13 +179,52 @@
   </si>
   <si>
     <t>78046552313</t>
+  </si>
+  <si>
+    <t>FIRST NAME</t>
+  </si>
+  <si>
+    <t>LAST NAME</t>
+  </si>
+  <si>
+    <t>PHONE</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>CT-1007</t>
+  </si>
+  <si>
+    <t>CT-1008</t>
+  </si>
+  <si>
+    <t>CT-1009</t>
+  </si>
+  <si>
+    <t>CT-1010</t>
+  </si>
+  <si>
+    <t>emmy.herman@miller.biz</t>
+  </si>
+  <si>
+    <t>&gt;ocb"8QN)C$=sIa"]Kp</t>
+  </si>
+  <si>
+    <t>elva.torphy@yahoo.com</t>
+  </si>
+  <si>
+    <t>VR%RzRqQRxD[.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,6 +242,20 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF98C379"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -224,10 +278,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -256,8 +311,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -589,9 +649,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF78ECA-9F9C-408E-8B71-24EBCB9A0622}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="6" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{B0308FEC-1770-4F1D-BB0B-F48CC96B8527}"/>
+  </hyperlinks>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A74B6D-8FA4-4011-9C72-01FBA93CFAED}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -601,7 +768,7 @@
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -627,7 +794,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -653,7 +820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -679,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -705,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -731,7 +898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -757,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -783,7 +950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -809,7 +976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -835,7 +1002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -861,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -894,12 +1061,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D587F36B-31B9-45A1-B9D4-E7990020F21E}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -922,7 +1089,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB5C55E-2D61-448B-9643-1957C93D0AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA1CE0B-B0BD-4091-A6FC-F25A34912F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="22245" windowHeight="15585" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
-    <sheet name="EBAC_MASSAS" sheetId="3" r:id="rId1"/>
+    <sheet name="My Demo App" sheetId="3" r:id="rId1"/>
     <sheet name="USUARIO" sheetId="1" r:id="rId2"/>
     <sheet name="USUARIO_SECUNDARIO" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="58">
   <si>
     <t>TAG</t>
   </si>
@@ -190,9 +190,6 @@
     <t>PHONE</t>
   </si>
   <si>
-    <t>EMAIL</t>
-  </si>
-  <si>
     <t>PASSWORD</t>
   </si>
   <si>
@@ -208,23 +205,20 @@
     <t>CT-1010</t>
   </si>
   <si>
-    <t>emmy.herman@miller.biz</t>
-  </si>
-  <si>
-    <t>&gt;ocb"8QN)C$=sIa"]Kp</t>
-  </si>
-  <si>
-    <t>elva.torphy@yahoo.com</t>
-  </si>
-  <si>
-    <t>VR%RzRqQRxD[.</t>
+    <t>EMAIL (UserName)</t>
+  </si>
+  <si>
+    <t>bob@example.com</t>
+  </si>
+  <si>
+    <t>10203040</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,12 +239,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF98C379"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
     </font>
     <font>
       <u/>
@@ -280,7 +268,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -311,10 +299,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -651,14 +641,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF78ECA-9F9C-408E-8B71-24EBCB9A0622}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="6" width="8.85546875" customWidth="1"/>
     <col min="7" max="7" width="28.5703125" customWidth="1"/>
     <col min="8" max="8" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,78 +668,79 @@
         <v>49</v>
       </c>
       <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="G3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{B0308FEC-1770-4F1D-BB0B-F48CC96B8527}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{956B44D1-76C6-4213-B0C0-1393AFF99062}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{0C84A6AA-D425-45EB-9B43-07DC17C535B7}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -758,7 +749,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A74B6D-8FA4-4011-9C72-01FBA93CFAED}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -768,7 +759,7 @@
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -794,7 +785,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -820,7 +811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -846,7 +837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -872,7 +863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -898,7 +889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -924,7 +915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -950,7 +941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -976,7 +967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1002,7 +993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -1028,7 +1019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -1064,9 +1055,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D587F36B-31B9-45A1-B9D4-E7990020F21E}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA1CE0B-B0BD-4091-A6FC-F25A34912F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFA57A8-CDFB-41B4-A5A5-68EFEC125D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="58">
   <si>
     <t>TAG</t>
   </si>
@@ -700,40 +700,88 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
+      <c r="G4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
+      <c r="G5" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>39</v>
       </c>
+      <c r="G6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>43</v>
       </c>
+      <c r="G7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
+      <c r="G8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
+      <c r="G9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>53</v>
       </c>
+      <c r="G10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -741,6 +789,14 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{956B44D1-76C6-4213-B0C0-1393AFF99062}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{0C84A6AA-D425-45EB-9B43-07DC17C535B7}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{C6AE981A-EF81-41AE-9C9C-F491DCBA2158}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{F9C424A8-4483-4473-8412-A8A44CDB7608}"/>
+    <hyperlink ref="G8" r:id="rId5" xr:uid="{88FCED1F-F23D-4A86-90C4-B5BD6A1F1979}"/>
+    <hyperlink ref="G10" r:id="rId6" xr:uid="{A0370A32-2528-4FE6-B203-BF19AF5DE404}"/>
+    <hyperlink ref="G5" r:id="rId7" xr:uid="{0A9F2B6D-CF4B-4216-90AF-08322D586481}"/>
+    <hyperlink ref="G7" r:id="rId8" xr:uid="{C805D7C8-DD3E-4CA8-BC77-C73C2B397AC0}"/>
+    <hyperlink ref="G9" r:id="rId9" xr:uid="{08E61F1F-E532-4B16-A94E-31FBEDFF9050}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{E78C43AD-50AB-4F7B-AF68-3BC07262CA22}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\TREINAMENTO\src\test\resources\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\AUTOMACAO\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D76439-CC9C-46F5-84F3-D5FA12FD50D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D88D556-88E2-47CD-B6D1-C72F088F50BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="45" windowWidth="17715" windowHeight="10740" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="20370" yWindow="-75" windowWidth="20730" windowHeight="11040" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>TAG</t>
   </si>
@@ -63,48 +63,9 @@
     <t>CT-1002</t>
   </si>
   <si>
-    <t>CT-1003</t>
-  </si>
-  <si>
-    <t>CT-2001</t>
-  </si>
-  <si>
     <t>123456</t>
   </si>
   <si>
-    <t>CT-3002</t>
-  </si>
-  <si>
-    <t>CT-3001</t>
-  </si>
-  <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <t>Pix</t>
-  </si>
-  <si>
-    <t>Login com sucesso e Validação do App</t>
-  </si>
-  <si>
-    <t>Pix com sucesso</t>
-  </si>
-  <si>
-    <t>123457</t>
-  </si>
-  <si>
-    <t>Receber Pix com sucesso</t>
-  </si>
-  <si>
-    <t>CT-4001</t>
-  </si>
-  <si>
-    <t>Investimento</t>
-  </si>
-  <si>
-    <t>Investimento com sucesso</t>
-  </si>
-  <si>
     <t>PID</t>
   </si>
   <si>
@@ -114,77 +75,71 @@
     <t>VALOR</t>
   </si>
   <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>7000</t>
-  </si>
-  <si>
     <t>5000</t>
   </si>
   <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>27589316857</t>
-  </si>
-  <si>
     <t>77589316857</t>
   </si>
   <si>
-    <t>Realizar login com CPF válido</t>
-  </si>
-  <si>
-    <t>Realizar login com CPF inválido</t>
-  </si>
-  <si>
-    <t>Validar logout com sucesso</t>
-  </si>
-  <si>
-    <t>CT-1004</t>
-  </si>
-  <si>
-    <t>Validar flag Lembrar CPF</t>
-  </si>
-  <si>
     <t>CT-1005</t>
   </si>
   <si>
-    <t>Validar tentar logar logar com CPF válido e Senha inválida</t>
-  </si>
-  <si>
-    <t>654987</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>CT-1006</t>
   </si>
   <si>
     <t>Validar tentar logar com CPF com Reject</t>
   </si>
   <si>
-    <t>USUARIO_SECUNDARIO</t>
-  </si>
-  <si>
-    <t>78046552313</t>
+    <t>Validar Login</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>CIDADE ORIGEM</t>
+  </si>
+  <si>
+    <t>CIDADE DESTINO</t>
+  </si>
+  <si>
+    <t>DATA INICIO</t>
+  </si>
+  <si>
+    <t>DATA FIM</t>
+  </si>
+  <si>
+    <t>teste15.4win@gmail.com</t>
+  </si>
+  <si>
+    <t>Teste15@4win</t>
+  </si>
+  <si>
+    <t>Validar pesquisar viagem</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Foz de Iguaçu</t>
+  </si>
+  <si>
+    <t>HOTEL SELECIONADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arcelona Hotel </t>
+  </si>
+  <si>
+    <t>Validar Hospedagens</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,6 +157,20 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -224,10 +193,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -256,8 +226,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -590,44 +568,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A74B6D-8FA4-4011-9C72-01FBA93CFAED}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -635,25 +625,18 @@
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -661,236 +644,240 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="str">
+        <f t="shared" ref="H3:H11" ca="1" si="0">DAY(L3) &amp; ""</f>
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <f t="shared" ref="I3:I11" ca="1" si="1">DAY(M3) &amp; ""</f>
+        <v>14</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="11">
+        <f ca="1">TODAY()+5</f>
+        <v>45836</v>
+      </c>
+      <c r="M3" s="11">
+        <f ca="1">TODAY()+21</f>
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="I4" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L4" s="11">
+        <f ca="1">TODAY()+6</f>
+        <v>45837</v>
+      </c>
+      <c r="M4" s="11">
+        <f ca="1">TODAY()+22</f>
+        <v>45853</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="I5" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L5" s="11">
+        <f ca="1">TODAY()+7</f>
+        <v>45838</v>
+      </c>
+      <c r="M5" s="11">
+        <f ca="1">TODAY()+23</f>
+        <v>45854</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
         <v>28</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="I6" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="L6" s="11">
+        <f t="shared" ref="L6:L11" ca="1" si="2">TODAY()+5</f>
+        <v>45836</v>
+      </c>
+      <c r="M6" s="11">
+        <f t="shared" ref="M6:M10" ca="1" si="3">TODAY()+20</f>
+        <v>45851</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="L7" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>45836</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" ref="M7" ca="1" si="4">TODAY()+21</f>
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="I8" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>15</v>
       </c>
-      <c r="D5" s="5">
-        <v>77589316857</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="L8" s="11">
+        <f t="shared" ref="L8" ca="1" si="5">TODAY()+6</f>
+        <v>45837</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" ref="M8" ca="1" si="6">TODAY()+22</f>
+        <v>45853</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="I9" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L9" s="11">
+        <f t="shared" ref="L9" ca="1" si="7">TODAY()+7</f>
+        <v>45838</v>
+      </c>
+      <c r="M9" s="11">
+        <f t="shared" ref="M9" ca="1" si="8">TODAY()+23</f>
+        <v>45854</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="I10" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="L10" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>45836</v>
+      </c>
+      <c r="M10" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>45851</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C11" s="6"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="I11" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5">
-        <v>77589316857</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="5">
-        <v>38627653933</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="5">
-        <v>77589316857</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="L11" s="11">
+        <f t="shared" ca="1" si="2"/>
+        <v>45836</v>
+      </c>
+      <c r="M11" s="11">
+        <f t="shared" ref="M11" ca="1" si="9">TODAY()+21</f>
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{C50C29E9-B45A-48BE-9DC0-38B607D8D8C2}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{A382BB8E-AED9-4AC0-BF5E-45468BD94C08}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -916,33 +903,33 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\AUTOMACAO\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D88D556-88E2-47CD-B6D1-C72F088F50BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03DD2F7-96BF-47A0-A4A1-E60E6B2F3033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-75" windowWidth="20730" windowHeight="11040" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>TAG</t>
   </si>
@@ -133,6 +133,18 @@
   </si>
   <si>
     <t>Barcelona</t>
+  </si>
+  <si>
+    <t>CT-1007</t>
+  </si>
+  <si>
+    <t>CT-1008</t>
+  </si>
+  <si>
+    <t>Validar Aluguel de carros</t>
+  </si>
+  <si>
+    <t>Beto</t>
   </si>
 </sst>
 </file>
@@ -708,11 +720,18 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="12"/>
+      <c r="F5" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="G5" s="12"/>
       <c r="H5" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -732,9 +751,15 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="6"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="12"/>
+      <c r="F6" s="12" t="s">
+        <v>35</v>
+      </c>
       <c r="G6" s="12"/>
       <c r="H6" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -754,6 +779,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="12"/>
@@ -776,6 +802,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="12"/>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\AUTOMACAO\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03DD2F7-96BF-47A0-A4A1-E60E6B2F3033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F35787-BB15-4EEC-AC0F-88E566F003C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-75" windowWidth="20730" windowHeight="11040" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -668,22 +668,22 @@
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" ref="H3:H11" ca="1" si="0">DAY(L3) &amp; ""</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1" t="str">
         <f t="shared" ref="I3:I11" ca="1" si="1">DAY(M3) &amp; ""</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L3" s="11">
         <f ca="1">TODAY()+5</f>
-        <v>45836</v>
+        <v>45838</v>
       </c>
       <c r="M3" s="11">
         <f ca="1">TODAY()+21</f>
-        <v>45852</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -704,19 +704,19 @@
       <c r="G4" s="12"/>
       <c r="H4" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L4" s="11">
         <f ca="1">TODAY()+6</f>
-        <v>45837</v>
+        <v>45839</v>
       </c>
       <c r="M4" s="11">
         <f ca="1">TODAY()+22</f>
-        <v>45853</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -735,19 +735,19 @@
       <c r="G5" s="12"/>
       <c r="H5" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L5" s="11">
         <f ca="1">TODAY()+7</f>
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="M5" s="11">
         <f ca="1">TODAY()+23</f>
-        <v>45854</v>
+        <v>45856</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -763,19 +763,19 @@
       <c r="G6" s="12"/>
       <c r="H6" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" ref="L6:L11" ca="1" si="2">TODAY()+5</f>
-        <v>45836</v>
+        <v>45838</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" ref="M6:M10" ca="1" si="3">TODAY()+20</f>
-        <v>45851</v>
+        <v>45853</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -786,19 +786,19 @@
       <c r="G7" s="12"/>
       <c r="H7" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>45836</v>
+        <v>45838</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" ref="M7" ca="1" si="4">TODAY()+21</f>
-        <v>45852</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -809,19 +809,19 @@
       <c r="G8" s="12"/>
       <c r="H8" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L8" s="11">
         <f t="shared" ref="L8" ca="1" si="5">TODAY()+6</f>
-        <v>45837</v>
+        <v>45839</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" ref="M8" ca="1" si="6">TODAY()+22</f>
-        <v>45853</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -832,19 +832,19 @@
       <c r="G9" s="12"/>
       <c r="H9" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L9" s="11">
         <f t="shared" ref="L9" ca="1" si="7">TODAY()+7</f>
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="M9" s="11">
         <f t="shared" ref="M9" ca="1" si="8">TODAY()+23</f>
-        <v>45854</v>
+        <v>45856</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -855,19 +855,19 @@
       <c r="G10" s="12"/>
       <c r="H10" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L10" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>45836</v>
+        <v>45838</v>
       </c>
       <c r="M10" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>45851</v>
+        <v>45853</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -878,19 +878,19 @@
       <c r="G11" s="12"/>
       <c r="H11" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L11" s="11">
         <f t="shared" ca="1" si="2"/>
-        <v>45836</v>
+        <v>45838</v>
       </c>
       <c r="M11" s="11">
         <f t="shared" ref="M11" ca="1" si="9">TODAY()+21</f>
-        <v>45852</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\AUTOMACAO\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F35787-BB15-4EEC-AC0F-88E566F003C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68C8DFF-7E6A-481A-B9BC-7E7520C98BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="25035" yWindow="45" windowWidth="16050" windowHeight="10905" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -584,8 +584,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="8" bestFit="1" customWidth="1"/>
@@ -704,15 +704,15 @@
       <c r="G4" s="12"/>
       <c r="H4" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I4" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>17</v>
       </c>
       <c r="L4" s="11">
-        <f ca="1">TODAY()+6</f>
-        <v>45839</v>
+        <f ca="1">TODAY()+5</f>
+        <v>45838</v>
       </c>
       <c r="M4" s="11">
         <f ca="1">TODAY()+22</f>
@@ -735,15 +735,15 @@
       <c r="G5" s="12"/>
       <c r="H5" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>18</v>
       </c>
       <c r="L5" s="11">
-        <f ca="1">TODAY()+7</f>
-        <v>45840</v>
+        <f ca="1">TODAY()+4</f>
+        <v>45837</v>
       </c>
       <c r="M5" s="11">
         <f ca="1">TODAY()+23</f>
@@ -809,18 +809,18 @@
       <c r="G8" s="12"/>
       <c r="H8" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>17</v>
       </c>
       <c r="L8" s="11">
-        <f t="shared" ref="L8" ca="1" si="5">TODAY()+6</f>
-        <v>45839</v>
+        <f ca="1">TODAY()+4</f>
+        <v>45837</v>
       </c>
       <c r="M8" s="11">
-        <f t="shared" ref="M8" ca="1" si="6">TODAY()+22</f>
+        <f t="shared" ref="M8" ca="1" si="5">TODAY()+22</f>
         <v>45855</v>
       </c>
     </row>
@@ -832,18 +832,18 @@
       <c r="G9" s="12"/>
       <c r="H9" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>18</v>
       </c>
       <c r="L9" s="11">
-        <f t="shared" ref="L9" ca="1" si="7">TODAY()+7</f>
-        <v>45840</v>
+        <f ca="1">TODAY()+4</f>
+        <v>45837</v>
       </c>
       <c r="M9" s="11">
-        <f t="shared" ref="M9" ca="1" si="8">TODAY()+23</f>
+        <f t="shared" ref="M9" ca="1" si="6">TODAY()+23</f>
         <v>45856</v>
       </c>
     </row>
@@ -889,7 +889,7 @@
         <v>45838</v>
       </c>
       <c r="M11" s="11">
-        <f t="shared" ref="M11" ca="1" si="9">TODAY()+21</f>
+        <f t="shared" ref="M11" ca="1" si="7">TODAY()+21</f>
         <v>45854</v>
       </c>
     </row>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\AUTOMACAO\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68C8DFF-7E6A-481A-B9BC-7E7520C98BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4301DA-879E-4307-A331-6F873690A6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25035" yWindow="45" windowWidth="16050" windowHeight="10905" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="25065" yWindow="45" windowWidth="16020" windowHeight="10905" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>TAG</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Beto</t>
+  </si>
+  <si>
+    <t>CT-1003</t>
+  </si>
+  <si>
+    <t>Validar fluxo Selecionar voo So Ida para 1 viajante</t>
   </si>
 </sst>
 </file>
@@ -580,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A74B6D-8FA4-4011-9C72-01FBA93CFAED}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
@@ -667,11 +673,11 @@
         <v>27</v>
       </c>
       <c r="H3" s="1" t="str">
-        <f t="shared" ref="H3:H11" ca="1" si="0">DAY(L3) &amp; ""</f>
+        <f t="shared" ref="H3:H12" ca="1" si="0">DAY(L3) &amp; ""</f>
         <v>30</v>
       </c>
       <c r="I3" s="1" t="str">
-        <f t="shared" ref="I3:I11" ca="1" si="1">DAY(M3) &amp; ""</f>
+        <f t="shared" ref="I3:I12" ca="1" si="1">DAY(M3) &amp; ""</f>
         <v>16</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -688,101 +694,113 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>30</v>
+      <c r="C4" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="12"/>
+        <v>26</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="H4" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="H4" ca="1" si="2">DAY(L4) &amp; ""</f>
         <v>30</v>
       </c>
       <c r="I4" s="1" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <f t="shared" ref="I4" ca="1" si="3">DAY(M4) &amp; ""</f>
+        <v>16</v>
       </c>
       <c r="L4" s="11">
         <f ca="1">TODAY()+5</f>
         <v>45838</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">TODAY()+22</f>
-        <v>45855</v>
+        <f ca="1">TODAY()+21</f>
+        <v>45854</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L5" s="11">
-        <f ca="1">TODAY()+4</f>
-        <v>45837</v>
+        <f ca="1">TODAY()+5</f>
+        <v>45838</v>
       </c>
       <c r="M5" s="11">
-        <f ca="1">TODAY()+23</f>
-        <v>45856</v>
+        <f ca="1">TODAY()+22</f>
+        <v>45855</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="6"/>
+        <v>32</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="12" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L6" s="11">
-        <f t="shared" ref="L6:L11" ca="1" si="2">TODAY()+5</f>
-        <v>45838</v>
+        <f ca="1">TODAY()+4</f>
+        <v>45837</v>
       </c>
       <c r="M6" s="11">
-        <f t="shared" ref="M6:M10" ca="1" si="3">TODAY()+20</f>
-        <v>45853</v>
+        <f ca="1">TODAY()+23</f>
+        <v>45856</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="12"/>
+      <c r="F7" s="12" t="s">
+        <v>35</v>
+      </c>
       <c r="G7" s="12"/>
       <c r="H7" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -790,15 +808,15 @@
       </c>
       <c r="I7" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L7" s="11">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ref="L7:L12" ca="1" si="4">TODAY()+5</f>
         <v>45838</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" ref="M7" ca="1" si="4">TODAY()+21</f>
-        <v>45854</v>
+        <f t="shared" ref="M7:M11" ca="1" si="5">TODAY()+20</f>
+        <v>45853</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -809,19 +827,19 @@
       <c r="G8" s="12"/>
       <c r="H8" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L8" s="11">
-        <f ca="1">TODAY()+4</f>
-        <v>45837</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45838</v>
       </c>
       <c r="M8" s="11">
-        <f t="shared" ref="M8" ca="1" si="5">TODAY()+22</f>
-        <v>45855</v>
+        <f t="shared" ref="M8" ca="1" si="6">TODAY()+21</f>
+        <v>45854</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -836,15 +854,15 @@
       </c>
       <c r="I9" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L9" s="11">
         <f ca="1">TODAY()+4</f>
         <v>45837</v>
       </c>
       <c r="M9" s="11">
-        <f t="shared" ref="M9" ca="1" si="6">TODAY()+23</f>
-        <v>45856</v>
+        <f t="shared" ref="M9" ca="1" si="7">TODAY()+22</f>
+        <v>45855</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -855,24 +873,24 @@
       <c r="G10" s="12"/>
       <c r="H10" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L10" s="11">
-        <f t="shared" ca="1" si="2"/>
-        <v>45838</v>
+        <f ca="1">TODAY()+4</f>
+        <v>45837</v>
       </c>
       <c r="M10" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>45853</v>
+        <f t="shared" ref="M10" ca="1" si="8">TODAY()+23</f>
+        <v>45856</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C11" s="6"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
@@ -882,20 +900,43 @@
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L11" s="11">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v>45838</v>
       </c>
       <c r="M11" s="11">
-        <f t="shared" ref="M11" ca="1" si="7">TODAY()+21</f>
-        <v>45854</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>45853</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C12" s="6"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
+      <c r="H12" s="1" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="I12" s="1" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L12" s="11">
+        <f t="shared" ca="1" si="4"/>
+        <v>45838</v>
+      </c>
+      <c r="M12" s="11">
+        <f t="shared" ref="M12" ca="1" si="9">TODAY()+21</f>
+        <v>45854</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\AUTOMACAO\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4301DA-879E-4307-A331-6F873690A6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4719EB6-234E-463A-BB87-7C2D6457CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25065" yWindow="45" windowWidth="16020" windowHeight="10905" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
@@ -716,15 +716,15 @@
       </c>
       <c r="I4" s="1" t="str">
         <f t="shared" ref="I4" ca="1" si="3">DAY(M4) &amp; ""</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" s="11">
-        <f ca="1">TODAY()+5</f>
+        <f ca="1">TODAY()+ 5</f>
         <v>45838</v>
       </c>
       <c r="M4" s="11">
-        <f ca="1">TODAY()+21</f>
-        <v>45854</v>
+        <f ca="1">TODAY()+22</f>
+        <v>45855</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\AUTOMACAO\javaMobileAppiumTests\src\test\resources\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4719EB6-234E-463A-BB87-7C2D6457CC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F116E5F3-556C-488E-86AE-B7BB86F8AEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25065" yWindow="45" windowWidth="16020" windowHeight="10905" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
   <si>
     <t>TAG</t>
   </si>
@@ -151,13 +151,49 @@
   </si>
   <si>
     <t>Validar fluxo Selecionar voo So Ida para 1 viajante</t>
+  </si>
+  <si>
+    <t>CT-1004</t>
+  </si>
+  <si>
+    <t>CT-1009</t>
+  </si>
+  <si>
+    <t>CT-1010</t>
+  </si>
+  <si>
+    <t>CT-1011</t>
+  </si>
+  <si>
+    <t>CT-1012</t>
+  </si>
+  <si>
+    <t>CT-1013</t>
+  </si>
+  <si>
+    <t>CT-1014</t>
+  </si>
+  <si>
+    <t>CT-1015</t>
+  </si>
+  <si>
+    <t>CT-1016</t>
+  </si>
+  <si>
+    <t>CT-1017</t>
+  </si>
+  <si>
+    <t>CT-1018</t>
+  </si>
+  <si>
+    <t>CT-1019</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,14 +203,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -213,17 +241,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -244,11 +269,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -586,16 +611,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A74B6D-8FA4-4011-9C72-01FBA93CFAED}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="23.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.28515625" style="2" customWidth="1"/>
@@ -613,22 +638,22 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -642,17 +667,17 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -664,32 +689,32 @@
       <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>27</v>
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" ref="H3:H12" ca="1" si="0">DAY(L3) &amp; ""</f>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I3" s="1" t="str">
         <f t="shared" ref="I3:I12" ca="1" si="1">DAY(M3) &amp; ""</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="10">
         <f ca="1">TODAY()+5</f>
-        <v>45838</v>
-      </c>
-      <c r="M3" s="11">
+        <v>45842</v>
+      </c>
+      <c r="M3" s="10">
         <f ca="1">TODAY()+21</f>
-        <v>45854</v>
+        <v>45858</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -702,241 +727,338 @@
       <c r="C4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="12" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>27</v>
       </c>
       <c r="H4" s="1" t="str">
         <f t="shared" ref="H4" ca="1" si="2">DAY(L4) &amp; ""</f>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I4" s="1" t="str">
         <f t="shared" ref="I4" ca="1" si="3">DAY(M4) &amp; ""</f>
-        <v>17</v>
-      </c>
-      <c r="L4" s="11">
+        <v>21</v>
+      </c>
+      <c r="L4" s="10">
         <f ca="1">TODAY()+ 5</f>
-        <v>45838</v>
-      </c>
-      <c r="M4" s="11">
+        <v>45842</v>
+      </c>
+      <c r="M4" s="10">
         <f ca="1">TODAY()+22</f>
-        <v>45855</v>
+        <v>45859</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="12" t="s">
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="11"/>
       <c r="H5" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="L5" s="11">
+        <v>21</v>
+      </c>
+      <c r="L5" s="10">
         <f ca="1">TODAY()+5</f>
-        <v>45838</v>
-      </c>
-      <c r="M5" s="11">
+        <v>45842</v>
+      </c>
+      <c r="M5" s="10">
         <f ca="1">TODAY()+22</f>
-        <v>45855</v>
+        <v>45859</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="12" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="11"/>
       <c r="H6" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I6" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="L6" s="11">
+        <v>22</v>
+      </c>
+      <c r="L6" s="10">
         <f ca="1">TODAY()+4</f>
-        <v>45837</v>
-      </c>
-      <c r="M6" s="11">
+        <v>45841</v>
+      </c>
+      <c r="M6" s="10">
         <f ca="1">TODAY()+23</f>
-        <v>45856</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="12"/>
+      <c r="G7" s="11"/>
       <c r="H7" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I7" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L7" s="11">
+        <v>19</v>
+      </c>
+      <c r="L7" s="10">
         <f t="shared" ref="L7:L12" ca="1" si="4">TODAY()+5</f>
-        <v>45838</v>
-      </c>
-      <c r="M7" s="11">
+        <v>45842</v>
+      </c>
+      <c r="M7" s="10">
         <f t="shared" ref="M7:M11" ca="1" si="5">TODAY()+20</f>
-        <v>45853</v>
+        <v>45857</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
       <c r="H8" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I8" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="L8" s="11">
+        <v>20</v>
+      </c>
+      <c r="L8" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>45838</v>
-      </c>
-      <c r="M8" s="11">
+        <v>45842</v>
+      </c>
+      <c r="M8" s="10">
         <f t="shared" ref="M8" ca="1" si="6">TODAY()+21</f>
-        <v>45854</v>
+        <v>45858</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I9" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="L9" s="11">
+        <v>21</v>
+      </c>
+      <c r="L9" s="10">
         <f ca="1">TODAY()+4</f>
-        <v>45837</v>
-      </c>
-      <c r="M9" s="11">
+        <v>45841</v>
+      </c>
+      <c r="M9" s="10">
         <f t="shared" ref="M9" ca="1" si="7">TODAY()+22</f>
-        <v>45855</v>
+        <v>45859</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="6"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="L10" s="11">
+        <v>22</v>
+      </c>
+      <c r="L10" s="10">
         <f ca="1">TODAY()+4</f>
-        <v>45837</v>
-      </c>
-      <c r="M10" s="11">
+        <v>45841</v>
+      </c>
+      <c r="M10" s="10">
         <f t="shared" ref="M10" ca="1" si="8">TODAY()+23</f>
-        <v>45856</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="6"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L11" s="11">
+        <v>19</v>
+      </c>
+      <c r="L11" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>45838</v>
-      </c>
-      <c r="M11" s="11">
+        <v>45842</v>
+      </c>
+      <c r="M11" s="10">
         <f t="shared" ca="1" si="5"/>
-        <v>45853</v>
+        <v>45857</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="6"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="1" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I12" s="1" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="L12" s="11">
+        <v>20</v>
+      </c>
+      <c r="L12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>45838</v>
-      </c>
-      <c r="M12" s="11">
+        <v>45842</v>
+      </c>
+      <c r="M12" s="10">
         <f t="shared" ref="M12" ca="1" si="9">TODAY()+21</f>
-        <v>45854</v>
+        <v>45858</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -964,16 +1086,16 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -984,19 +1106,19 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
     </row>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\MobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F116E5F3-556C-488E-86AE-B7BB86F8AEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C5A9D5-FDFE-45CA-B82C-BEBA74FBE544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>SENHA</t>
   </si>
   <si>
-    <t>CT-1001</t>
-  </si>
-  <si>
     <t>Login</t>
   </si>
   <si>
@@ -187,6 +184,9 @@
   </si>
   <si>
     <t>CT-1019</t>
+  </si>
+  <si>
+    <t>CT-01.1</t>
   </si>
 </sst>
 </file>
@@ -616,7 +616,7 @@
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="45.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="7" bestFit="1" customWidth="1"/>
@@ -639,63 +639,63 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" ref="H3:H12" ca="1" si="0">DAY(L3) &amp; ""</f>
@@ -706,34 +706,34 @@
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L3" s="10">
         <f ca="1">TODAY()+5</f>
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="M3" s="10">
         <f ca="1">TODAY()+21</f>
-        <v>45858</v>
+        <v>46011</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="H4" s="1" t="str">
         <f t="shared" ref="H4" ca="1" si="2">DAY(L4) &amp; ""</f>
@@ -745,27 +745,27 @@
       </c>
       <c r="L4" s="10">
         <f ca="1">TODAY()+ 5</f>
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="M4" s="10">
         <f ca="1">TODAY()+22</f>
-        <v>45859</v>
+        <v>46012</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="1" t="str">
@@ -778,27 +778,27 @@
       </c>
       <c r="L5" s="10">
         <f ca="1">TODAY()+5</f>
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="M5" s="10">
         <f ca="1">TODAY()+22</f>
-        <v>45859</v>
+        <v>46012</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="1" t="str">
@@ -811,25 +811,25 @@
       </c>
       <c r="L6" s="10">
         <f ca="1">TODAY()+4</f>
-        <v>45841</v>
+        <v>45994</v>
       </c>
       <c r="M6" s="10">
         <f ca="1">TODAY()+23</f>
-        <v>45860</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="1" t="str">
@@ -842,19 +842,19 @@
       </c>
       <c r="L7" s="10">
         <f t="shared" ref="L7:L12" ca="1" si="4">TODAY()+5</f>
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="M7" s="10">
         <f t="shared" ref="M7:M11" ca="1" si="5">TODAY()+20</f>
-        <v>45857</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4"/>
@@ -871,19 +871,19 @@
       </c>
       <c r="L8" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="M8" s="10">
         <f t="shared" ref="M8" ca="1" si="6">TODAY()+21</f>
-        <v>45858</v>
+        <v>46011</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4"/>
@@ -900,19 +900,19 @@
       </c>
       <c r="L9" s="10">
         <f ca="1">TODAY()+4</f>
-        <v>45841</v>
+        <v>45994</v>
       </c>
       <c r="M9" s="10">
         <f t="shared" ref="M9" ca="1" si="7">TODAY()+22</f>
-        <v>45859</v>
+        <v>46012</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4"/>
@@ -929,19 +929,19 @@
       </c>
       <c r="L10" s="10">
         <f ca="1">TODAY()+4</f>
-        <v>45841</v>
+        <v>45994</v>
       </c>
       <c r="M10" s="10">
         <f t="shared" ref="M10" ca="1" si="8">TODAY()+23</f>
-        <v>45860</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4"/>
@@ -958,19 +958,19 @@
       </c>
       <c r="L11" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="M11" s="10">
         <f t="shared" ca="1" si="5"/>
-        <v>45857</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="8"/>
@@ -987,77 +987,77 @@
       </c>
       <c r="L12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>45842</v>
+        <v>45995</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" ref="M12" ca="1" si="9">TODAY()+21</f>
-        <v>45858</v>
+        <v>46011</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1093,33 +1093,33 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\MobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C5A9D5-FDFE-45CA-B82C-BEBA74FBE544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E716C0-77DD-4EC5-B615-71EF84359454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Login</t>
   </si>
   <si>
-    <t>CT-1002</t>
-  </si>
-  <si>
     <t>123456</t>
   </si>
   <si>
@@ -187,6 +184,9 @@
   </si>
   <si>
     <t>CT-01.1</t>
+  </si>
+  <si>
+    <t>CT-02.1</t>
   </si>
 </sst>
 </file>
@@ -639,63 +639,63 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" ref="H3:H12" ca="1" si="0">DAY(L3) &amp; ""</f>
@@ -706,7 +706,7 @@
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L3" s="10">
         <f ca="1">TODAY()+5</f>
@@ -719,21 +719,21 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="H4" s="1" t="str">
         <f t="shared" ref="H4" ca="1" si="2">DAY(L4) &amp; ""</f>
@@ -754,18 +754,18 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="1" t="str">
@@ -787,18 +787,18 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="1" t="str">
@@ -820,7 +820,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -829,7 +829,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="1" t="str">
@@ -851,7 +851,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -880,7 +880,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -967,7 +967,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>5</v>
@@ -1093,33 +1093,33 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\MobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21F861C-E790-4A5B-8CFE-313B6DD8DEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38635E5-10C2-4A62-928D-C1364DC48A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="1" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" tabRatio="547" activeTab="1" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="TBL_CENARIOS" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="459">
   <si>
     <t>FEATURE</t>
   </si>
@@ -1494,7 +1494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1536,12 +1536,6 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1550,7 +1544,15 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="18">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1562,74 +1564,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1691,21 +1625,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}" name="Tabela1" displayName="Tabela1" ref="A1:J10" totalsRowShown="0" headerRowDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}" name="Tabela1" displayName="Tabela1" ref="A1:J10" totalsRowShown="0" headerRowDxfId="17">
   <autoFilter ref="A1:J10" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J9">
     <sortCondition ref="B1:B9"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{240E8A87-6B9D-469C-96B4-1ADF1A1B51F9}" name="SEQ" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{A5A7BB75-84B5-4E70-9BA0-C776DE14C91C}" name="ID_CENARIO" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{240E8A87-6B9D-469C-96B4-1ADF1A1B51F9}" name="SEQ" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{A5A7BB75-84B5-4E70-9BA0-C776DE14C91C}" name="ID_CENARIO" dataDxfId="15"/>
     <tableColumn id="3" xr3:uid="{F8063F50-952C-4E2D-A074-3E8144115D2A}" name="NOME"/>
-    <tableColumn id="4" xr3:uid="{8DDE6FAA-E6CF-4246-9642-56091E15680F}" name="FEATURE" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{C3B59964-FB20-45D3-83A9-C8E4430D8B4D}" name="ID_MASSA" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{BD63E5A8-2387-4287-9027-FC33B730B309}" name="EMAIL" dataDxfId="18">
+    <tableColumn id="4" xr3:uid="{8DDE6FAA-E6CF-4246-9642-56091E15680F}" name="FEATURE" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{C3B59964-FB20-45D3-83A9-C8E4430D8B4D}" name="ID_MASSA" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{BD63E5A8-2387-4287-9027-FC33B730B309}" name="EMAIL" dataDxfId="12">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BC16A81B-1C0C-4894-BA93-501560053E29}" name="SENHA" dataDxfId="17">
+    <tableColumn id="10" xr3:uid="{BC16A81B-1C0C-4894-BA93-501560053E29}" name="SENHA" dataDxfId="11">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{B89F7EB3-E18D-4B11-80BD-03538541B067}" name="CARACTERISTICAS"/>
@@ -1717,18 +1651,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{63113370-7307-4D9F-A005-28D4D96B86FA}" name="Tabela15" displayName="Tabela15" ref="A1:I9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:I9" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{63113370-7307-4D9F-A005-28D4D96B86FA}" name="Tabela15" displayName="Tabela15" ref="A1:I10" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I10" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{76DED8C3-CAED-4F92-BEFF-1D1672477026}" name="SEQ" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{1B34B2D7-6E01-4503-BF80-E6FA0B5264BE}" name="ID_MASSA" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{2A87BFE1-F7B7-4CC5-BF83-A1ACA0AA1B71}" name="NOME_COMPLETO" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{CEE84FB7-6516-43D3-A087-5E2B5901F371}" name="NOME_USUARIO" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{A94F6B35-2950-495F-ABAD-80D52A635FCB}" name="EMAIL" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{C45F2582-248A-4FD2-93C4-DC5EE6FD9337}" name="SENHA" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{4A91FF1E-8039-4084-81C6-46AC93CD4987}" name="ID_USUARIO" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{76915B7C-C8DF-49DC-AE8C-85A8E195B653}" name="ID_CATEGORIA" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{7019F3A5-C393-4DF2-A287-B48B03B927F9}" name="ID_ARTIGO" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{76DED8C3-CAED-4F92-BEFF-1D1672477026}" name="SEQ" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1B34B2D7-6E01-4503-BF80-E6FA0B5264BE}" name="ID_MASSA" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{2A87BFE1-F7B7-4CC5-BF83-A1ACA0AA1B71}" name="NOME_COMPLETO" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{CEE84FB7-6516-43D3-A087-5E2B5901F371}" name="NOME_USUARIO" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{A94F6B35-2950-495F-ABAD-80D52A635FCB}" name="EMAIL" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{C45F2582-248A-4FD2-93C4-DC5EE6FD9337}" name="SENHA" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{4A91FF1E-8039-4084-81C6-46AC93CD4987}" name="ID_USUARIO" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{76915B7C-C8DF-49DC-AE8C-85A8E195B653}" name="ID_CATEGORIA" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{7019F3A5-C393-4DF2-A287-B48B03B927F9}" name="ID_ARTIGO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2314,8 +2248,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
+      <c r="A10" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>453</v>
@@ -2329,11 +2263,11 @@
       <c r="E10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="15" t="str">
+      <c r="F10" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
         <v>jean@test.com</v>
       </c>
-      <c r="G10" s="15" t="str">
+      <c r="G10" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
         <v>admin999</v>
       </c>
@@ -2349,18 +2283,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21F4E9FD-68D5-4E43-8196-C7334FA814AB}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="38.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2652,21 +2586,30 @@
       <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="E10" s="12"/>
+      <c r="I10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/src/test/resources/dados/MassaDados.xlsx
+++ b/src/test/resources/dados/MassaDados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\MobileAppiumTests\src\test\resources\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C57E9B-F086-4779-A2E8-2EF31B775E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15A6F3C-0F73-4BE8-B706-837484012AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="689" activeTab="2" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" tabRatio="689" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="TBL_CENARIOS" sheetId="3" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="101">
   <si>
     <t>FEATURE</t>
   </si>
@@ -339,6 +339,15 @@
   </si>
   <si>
     <t>jessica@test.com</t>
+  </si>
+  <si>
+    <t>CT-01.3</t>
+  </si>
+  <si>
+    <t>CT-01.4</t>
+  </si>
+  <si>
+    <t>CT-01.5</t>
   </si>
 </sst>
 </file>
@@ -409,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -458,6 +467,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -727,8 +745,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}" name="Tabela1" displayName="Tabela1" ref="A1:J29" totalsRowShown="0" headerRowDxfId="40">
-  <autoFilter ref="A1:J29" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}" name="Tabela1" displayName="Tabela1" ref="A1:J32" totalsRowShown="0" headerRowDxfId="40">
+  <autoFilter ref="A1:J32" xr:uid="{056F21A2-18B3-4119-B8E1-51F7C4D22D38}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{240E8A87-6B9D-469C-96B4-1ADF1A1B51F9}" name="SEQ" dataDxfId="39"/>
     <tableColumn id="2" xr3:uid="{A5A7BB75-84B5-4E70-9BA0-C776DE14C91C}" name="ID_CENARIO" dataDxfId="38"/>
@@ -1131,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F71858-38D3-4D97-A145-DA082D656605}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
@@ -1234,173 +1252,176 @@
       <c r="J3" s="9"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="B4" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="18" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
+        <v>teste@test.com</v>
+      </c>
+      <c r="G4" s="19" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
+        <v>admin999</v>
+      </c>
+      <c r="H4" s="20">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
+        <v>22222222222</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="18" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
+        <v>teste@test.com</v>
+      </c>
+      <c r="G5" s="19" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
+        <v>admin999</v>
+      </c>
+      <c r="H5" s="20">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
+        <v>22222222222</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="18" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
+        <v>teste@test.com</v>
+      </c>
+      <c r="G6" s="19" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
+        <v>admin999</v>
+      </c>
+      <c r="H6" s="20">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
+        <v>22222222222</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="str">
+      <c r="F7" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
         <v>admin@test.com</v>
       </c>
-      <c r="G4" s="10" t="str">
+      <c r="G7" s="10" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
         <v>admin999</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H7" s="17">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
         <v>99999999999</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="2" t="str">
+      <c r="F8" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
         <v>admin@test.com</v>
       </c>
-      <c r="G5" s="10" t="str">
+      <c r="G8" s="10" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
         <v>admin999</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H8" s="17">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
         <v>99999999999</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="2" t="str">
+      <c r="F9" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
         <v>admin@test.com</v>
       </c>
-      <c r="G6" s="10" t="str">
+      <c r="G9" s="10" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
         <v>admin999</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H9" s="17">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
         <v>99999999999</v>
       </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>teste@test.com</v>
-      </c>
-      <c r="G7" s="2" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
-        <v>admin999</v>
-      </c>
-      <c r="H7" s="3">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>22222222222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>teste@test.com</v>
-      </c>
-      <c r="G8" s="2" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
-        <v>admin999</v>
-      </c>
-      <c r="H8" s="3">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>22222222222</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="2" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>teste@test.com</v>
-      </c>
-      <c r="G9" s="2" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
-        <v>admin999</v>
-      </c>
-      <c r="H9" s="3">
-        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>22222222222</v>
-      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>16</v>
@@ -1420,10 +1441,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>16</v>
@@ -1443,10 +1464,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>16</v>
@@ -1466,10 +1487,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>16</v>
@@ -1489,17 +1510,17 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>71</v>
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>admin@test.com</v>
+        <v>teste@test.com</v>
       </c>
       <c r="G14" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
@@ -1507,22 +1528,22 @@
       </c>
       <c r="H14" s="3">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>99999999999</v>
+        <v>22222222222</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>admin@test.com</v>
+        <v>teste@test.com</v>
       </c>
       <c r="G15" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
@@ -1530,22 +1551,22 @@
       </c>
       <c r="H15" s="3">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>99999999999</v>
+        <v>22222222222</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>73</v>
+        <v>11</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F16" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>admin@test.com</v>
+        <v>teste@test.com</v>
       </c>
       <c r="G16" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
@@ -1553,15 +1574,15 @@
       </c>
       <c r="H16" s="3">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>99999999999</v>
+        <v>22222222222</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>14</v>
@@ -1581,10 +1602,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>14</v>
@@ -1604,17 +1625,17 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>teste@test.com</v>
+        <v>admin@test.com</v>
       </c>
       <c r="G19" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
@@ -1622,22 +1643,22 @@
       </c>
       <c r="H19" s="3">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>22222222222</v>
+        <v>99999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>teste@test.com</v>
+        <v>admin@test.com</v>
       </c>
       <c r="G20" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
@@ -1645,22 +1666,22 @@
       </c>
       <c r="H20" s="3">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>22222222222</v>
+        <v>99999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
-        <v>teste@test.com</v>
+        <v>admin@test.com</v>
       </c>
       <c r="G21" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
@@ -1668,15 +1689,15 @@
       </c>
       <c r="H21" s="3">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
-        <v>22222222222</v>
+        <v>99999999999</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>16</v>
@@ -1696,10 +1717,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>16</v>
@@ -1719,10 +1740,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>16</v>
@@ -1742,10 +1763,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>16</v>
@@ -1765,10 +1786,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>16</v>
@@ -1788,10 +1809,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>16</v>
@@ -1811,10 +1832,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>16</v>
@@ -1834,10 +1855,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>16</v>
@@ -1851,6 +1872,75 @@
         <v>admin999</v>
       </c>
       <c r="H29" s="3">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
+        <v>22222222222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
+        <v>teste@test.com</v>
+      </c>
+      <c r="G30" s="2" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
+        <v>admin999</v>
+      </c>
+      <c r="H30" s="3">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
+        <v>22222222222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
+        <v>teste@test.com</v>
+      </c>
+      <c r="G31" s="2" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
+        <v>admin999</v>
+      </c>
+      <c r="H31" s="3">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
+        <v>22222222222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>27</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],4,FALSE)</f>
+        <v>teste@test.com</v>
+      </c>
+      <c r="G32" s="2" t="str">
+        <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[ID_MASSA]:[SENHA]],5,FALSE)</f>
+        <v>admin999</v>
+      </c>
+      <c r="H32" s="3">
         <f>VLOOKUP(Tabela1[[#This Row],[ID_MASSA]],Tabela15[[#All],[ID_MASSA]:[ID_ARTIGO]],3,FALSE)</f>
         <v>22222222222</v>
       </c>
